--- a/uploadfiles/Type2.xlsx
+++ b/uploadfiles/Type2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\OneDrive\Desktop\Projects\Ideas\CLAUD\RecallTxtChecker\uploadfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4ACC4975-2607-4F33-AF83-D36E8212D4A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA58B42F-7739-4943-B046-585560AD8A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="32490" yWindow="1455" windowWidth="21600" windowHeight="11295" xr2:uid="{EF0E5BE2-3734-4FAD-A5E2-2F7A3160C899}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>1FTEW1LP9RKD33544</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t>Worth &amp; Co</t>
+  </si>
+  <si>
+    <t>1FTEW1LP9RKD33543</t>
   </si>
 </sst>
 </file>
@@ -442,7 +445,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/uploadfiles/Type2.xlsx
+++ b/uploadfiles/Type2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chris\OneDrive\Desktop\Projects\Ideas\CLAUD\RecallTxtChecker\uploadfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA58B42F-7739-4943-B046-585560AD8A3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0C007B-8E68-40C2-B398-C0AE2D0C5352}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32490" yWindow="1455" windowWidth="21600" windowHeight="11295" xr2:uid="{EF0E5BE2-3734-4FAD-A5E2-2F7A3160C899}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF0E5BE2-3734-4FAD-A5E2-2F7A3160C899}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,24 +36,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>1FTEW1LP9RKD33544</t>
   </si>
   <si>
-    <t>Allan Myers</t>
+    <t>1FTEW1LP9RKD33543</t>
   </si>
   <si>
-    <t>Worth &amp; Co</t>
-  </si>
-  <si>
-    <t>1FTEW1LP9RKD33543</t>
+    <t>#147</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -89,9 +89,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="6" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -429,23 +438,23 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" customWidth="1"/>
+    <col min="1" max="1" width="21.42578125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
+      <c r="A2" s="3">
+        <v>153</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
